--- a/ket_qua_cap_nhat_dangky.xlsx
+++ b/ket_qua_cap_nhat_dangky.xlsx
@@ -424,7 +424,7 @@
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="36" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="80" customWidth="1" min="11" max="11"/>
   </cols>
@@ -495,27 +495,23 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>178</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>501</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>12859499</v>
-      </c>
-      <c r="G2" t="n">
-        <v>5719711</v>
-      </c>
-      <c r="H2" t="n">
-        <v>8115987</v>
-      </c>
+        <v>14075190</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Hồ Văn Thọ &amp; Trần Thị Minh Thư</t>
+          <t>Bà Cao Thị Chi và Ông Nguyễn Thành</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -525,7 +521,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Cập nhật thành công | Cập nhật mã định danh CCCD - Hồ Văn Thọ: 066073008909 | Cập nhật mã định danh CCCD - Trần Thị Minh Thư: 066178007145 | Cập nhật lại thông tin GCN (id=1292385, soPhatHanh=AN 675030, trường=soVaoSo) | Đã update delta GCN: số/ngày vào sổ | Đã update cá nhân: Hồ Văn Thọ | Đã update cá nhân: Trần Thị Minh Thư | Đã update thửa đất: 24163.100017.100312 | Update TTĐK OK (json_wrapper_thongTinDangKy) | Đã gửi yêu cầu phân loại lại thửa: [1405368] | HSQ đã có file vừa là GCN vừa là giấy tờ nguồn gốc, bỏ qua</t>
+          <t>Cập nhật thành công | Lỗi phân loại: Thông tin đăng ký 14075190 có giấy chứng nhận 1234964_11 không có số vào sổ; Thông tin đăng ký 14075190 có giấy chứng nhận 1234964_11 không có ngayVaoSo | Thiếu: TINHHINHDANGKY.14075190|GIAYCHUNGNHAN.1234964_11|soVaoSo; TINHHINHDANGKY.14075190|GIAYCHUNGNHAN.1234964_11|ngayVaoSo | Cập nhật mã định danh CCCD - Nguyễn Thành: 066070008093 | Cập nhật mã định danh CCCD - Cao Thị Chi: 066170008633 | Cập nhật lại thông tin GCN (id=1234964, soPhatHanh=CM 596396, trường=ngayVaoSo,soVaoSo) | Cập nhật lại thông tin GCN 1234964: soVaoSo, ngayVaoSo | Cập nhật mã định danh cá nhân bằng delta: Nguyễn Thành = 066070008093 | Cập nhật mã định danh cá nhân bằng delta: Cao Thị Chi = 066170008633 | Đã update delta làm sạch: GCN/nguồn gốc/mã định danh/năm sinh | Không có lỗi HSQ, bỏ qua Get/Update HSQ | Đã gửi yêu cầu phân loại lại thửa: [1362880]</t>
         </is>
       </c>
     </row>
